--- a/data/游戏下载链接05-25.xlsx
+++ b/data/游戏下载链接05-25.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,185 +456,3700 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>月影杀/Kristala</t>
+          <t>神话时代：重述版/Age of Mythology: Retold（更新v100.19.10195）</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/1206410/7a5f71c05819e0102bb53f6429e018af6ba452b5/header_schinese.jpg?t=1777215800</t>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/1934680/header.jpg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://pan.baidu.com/share/init?surl=phQXTXmxIv-sbMZ2_I6peg&amp;pwd=c2r3</t>
+          <t>https://pan.baidu.com/share/init?surl=mPa4T_-hAszKCpBkpQqEjQ&amp;pwd=yyhi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cloud.189.cn/web/share?code=MveEJnayuQBv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9As7hd%EF%BC%89</t>
+          <t>https://cloud.189.cn/web/share?code=JvEJbaJJrYri%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aac5h%EF%BC%89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://pan.xunlei.com/s/VOrBWxtvtPcUBPXd7u2wr-XhA1?pwd=kb7i</t>
+          <t>https://pan.xunlei.com/s/VONcdvkTGMhPHi6ouiJAYApHA1?pwd=5kjh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>986532</t>
+          <t>447435</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.yyds567.com/40013.html</t>
+          <t>https://www.yyds567.com/24538.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>突袭5/Sudden Strike 5</t>
+          <t>YAR：被遗忘的王座/YAR: Forgotten Throne（更新Build.22638180）</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2808550/b605fb58a451cd8ff5928e5576c216e201106211/header.jpg?t=1777044622</t>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2669860/2de87a7e65cc01a54f0fa9661b3a143bee9ccd44/header.jpg?t=1762086019</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://pan.baidu.com/share/init?surl=4yJFHUHb0OLzoWsNWzGnNA&amp;pwd=rgws</t>
+          <t>https://pan.baidu.com/share/init?surl=VbEvL-MzjeO9WsoJdEF1bg&amp;pwd=re9g</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cloud.189.cn/web/share?code=q6fmQjRJzQvu%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A2suo%EF%BC%89</t>
+          <t>https://cloud.189.cn/web/share?code=ErIBVjB73mie%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ayjh4%EF%BC%89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://pan.xunlei.com/s/VOrBWRyP6LNI35zJHlG3d8rAA1?pwd=dmai</t>
+          <t>https://pan.xunlei.com/s/VOdM75ujsTOhqcUpQXR2pTwBA1?pwd=eiem</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>665562</t>
+          <t>789799</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.yyds567.com/40012.html</t>
+          <t>https://www.yyds567.com/38083.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>利润海：增量/Profit Sea Incremental</t>
+          <t>人性末日/HumanitZ（更新v1.03.B）</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/4461640/825d3731e8a201034f839517913db647a016c359/header.jpg?t=1774967620</t>
+          <t>https://shared.st.dl.eccdnx.com/store_item_assets/steam/apps/1766060/header.jpg?t=1732212002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://pan.baidu.com/share/init?surl=_YdnUxWW0q3oW85b83Pz3A&amp;pwd=pp4f</t>
+          <t>https://pan.baidu.com/share/init?surl=c9i3LNsqCsg9oGT3iKs0sA&amp;pwd=uyid</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://cloud.189.cn/web/share?code=FbAJzanmMjyi%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A7lrn%EF%BC%89</t>
+          <t>https://cloud.189.cn/web/share?code=A7ry2quIz22e%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A1xkz%EF%BC%89</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://pan.xunlei.com/s/VOrBW1IzFrVRHpb6FyOHL2HaA1?pwd=4aip</t>
+          <t>https://pan.xunlei.com/s/VONscRB0McXMCl2PNbRy1Ep8A1?pwd=qij9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>886532</t>
+          <t>963221</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.yyds567.com/40011.html</t>
+          <t>https://www.yyds567.com/23325.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>包裹配送模拟器/Parcel Delivery Simulator</t>
+          <t>幻兽帕鲁/Palworld（更新v0.7.3.90464）</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/4078230/7ffb52194bf760056b8f30a680027ec442aa90de/header.jpg?t=1776841683</t>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1623730/header_schinese.jpg?t=1728458632</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://pan.baidu.com/share/init?surl=IweH6rxXlw1uYQOKEMKqOA&amp;pwd=z2af</t>
+          <t>https://pan.baidu.com/share/init?surl=Ovsd1U_dYkcvMfK35nRh-A&amp;pwd=6gr3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://cloud.189.cn/web/share?code=UfMZfu6feAFf%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A6rh9%EF%BC%89</t>
+          <t>https://cloud.189.cn/web/share?code=iIZJbie67Jnq%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Avtr4%EF%BC%89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://pan.xunlei.com/s/VOrBV6RGBd-6pXpNmJvJ2Tb5A1?pwd=bqtu</t>
+          <t>https://pan.xunlei.com/s/VOWZHMlgbfQIeQeRtcYZl-D3A1?pwd=fq5i</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>986532</t>
+          <t>254777</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.yyds567.com/40010.html</t>
+          <t>https://www.yyds567.com/23545.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>死亡法典/CODEX MORTIS</t>
+          <t>最后的咒语/The Last Spell（更新v1.3.32.10）</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/4084120/50cf7a6315399de6325699ef70d9d99b430a2bd9/header.jpg?t=1776348636</t>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1105670/header.jpg?t=1736419027</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://pan.baidu.com/share/init?surl=kFRasXmBvNCYKSWhOT1bVw&amp;pwd=792h</t>
+          <t>https://pan.baidu.com/share/init?surl=5dScAyvQ31lWP2ssaj5EyQ&amp;pwd=h935</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://cloud.189.cn/web/share?code=qIVBJvM7veAf%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aycg1%EF%BC%89</t>
+          <t>https://cloud.189.cn/web/share?code=juyiIbfE3aUn%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Awt7g%EF%BC%89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://pan.xunlei.com/s/VOrBUQBfrYGZwcKBERGfDhn0A1?pwd=6h7n</t>
+          <t>https://pan.xunlei.com/s/VOQQeUqIOu07yEus2xG5-pomA1?pwd=ti2v</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>556699</t>
+          <t>623339</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.yyds567.com/40009.html</t>
+          <t>https://www.yyds567.com/15094.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>空中帝国/Airborne Empire（更新v1.0）</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2438680/header.jpg?t=1736954990</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=WJ2tqPSDYiC09CycvrsbNA&amp;pwd=qm9v</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=JRRvQ3R7nmIz%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Alk2h%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOH6x8cgNiS_epl83dPqkDTCA1?pwd=3na2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>301033</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/29830.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>仙王座协议/Cepheus Protocol（更新Build.22244860）</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://shared.cloudflare.steamstatic.com/store_item_assets/steam/apps/979640/header.jpg?t=1726445265</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=yv4rcJ5gQYD6QXKqbp3rlg&amp;pwd=8888</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=3uABNjMrmm2q%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Avi2e%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOBCZKP3_xJVETfVu7WHXfxyA1?pwd=ewpk</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>596631</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/24834.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>低杆高尔夫球场大亨/Under Par Golf Architect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2928410/1bf8775d5855fba332b36100249098291e8a9af5/header_alt_assets_0_schinese.jpg?t=1776873323</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=ydAwnBGEivNrQe4w2xo_5A&amp;pwd=8cfq</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=imauYzZJ3Yfm%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aa6es%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqx7zT7Bd-6pXpNmJv9xEGNA1?pwd=efh7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>895623</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40008.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>命运腐化/LUCKROT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3823650/f873f0fd540665e53943fac68b83d34e95e5cdba/header.jpg?t=1776651115</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=jm-kwU5a57vAy7_jOPK7Xw&amp;pwd=xkpx</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=7JjIrebANzMv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aewe1%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqx7Wt2y1b57H9mhJ6O5lGvA1?pwd=d5e9</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>369855</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40007.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>俄罗斯方块大师4/TETRIS THE GRAND MASTER 4 -ABSOLUTE EYE-</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3328480/header.jpg?t=1770178936</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=2nTYXJn4xleJJe2BU5MxVA&amp;pwd=7bg9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=e67BbujMju6b%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Asou8%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqx6sl9FrVRHpb6FyO8AT4ZA1?pwd=cef6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>235655</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/31868.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>勇士永存/Bylina</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2461440/5b35f51f9e5b43e6dbc80094c8ddc7ac16645ac0/header.jpg?t=1776877185</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=of_ELWbNQbttx0tUMkZaxA&amp;pwd=xm2w</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=7jUBryaeiIfa%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A1ypm%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqx6DRAuUW96dtxkAOMhL_5A1?pwd=vus5</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>986532</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40006.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>吸血鬼爬行者: 屠戮地牢的吸血鬼幸存者/Vampire Crawlers: The Turbo Wildcard from Vampire Survivors</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3265700/5590e42cab09dacabee973dd2c3e27ef12ed4950/header.jpg?t=1776925935</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=zWG3cCOUFe7aeWnvGtTWAw&amp;pwd=yy1a</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=2AZfee6fARN3%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aorj5%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqx5ilXhnZ2OUODS3GfW8l1A1?pwd=5r8p</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>369852</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40005.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>舒舒服服小岛时光/Cozy Island</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2918500/12c434ab54d9199fc50592cfa3b95fd7b53b6335/header_schinese.jpg?t=1776773063</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=ktkJfl8Gba9YfM5h2UBy0w&amp;pwd=8ac4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=VBjQniMzMVZn%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Azem9%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqs0Iaw-BFQbEMtQpP9F7PGA1?pwd=mj6a</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>235689</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40004.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>邪教之国/Cult Nation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3897540/e3e36df3bb77547a0369e57e3ab50338c80985f2/header.jpg?t=1776258175</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=Qrq6TGmNTsoDSKo8uL8YOQ&amp;pwd=mr7v</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=rMBbuuqeI7Fz%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A9aif%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqs-of7mX1wsNKBjslHIrZHA1?pwd=yceu</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>989865</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40003.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>击败所有Boss：放置游戏/Slay All Bosses: Idle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/4232600/30e025e85a3bd12feb5481fa337a3ac44aa987f8/header.jpg?t=1776194339</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=avseDIEtxvoJ25u3ZKj_HQ&amp;pwd=h4wg</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=uamqayEfqYbq%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Adkm3%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqs-GRfNaSZJ_52MyiDGur9A1?pwd=zcmx</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>895623</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40002.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>绿茵谷物语/Greenfield Valley</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/4291370/73e23eb2a3fea8c8b14f6ecd82e3ef083d1c1876/header.jpg?t=1775747947</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=NZejmOrl-fZTzvHGWrm5QQ&amp;pwd=ps8a</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=uuIfumqYjAje%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aav1v%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqrz5GC4OfWSgmtrj_vzHoMA1?pwd=hwzf</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>465985</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>余火守护者/The Ember Guardian</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3570060/1539eca7d0b7f43aaa7e0208f8e6d543b22244be/header.jpg?t=1776533389</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=GXG6EweorWCBQJ7bFkIDoQ&amp;pwd=ahi5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=MNJVruu6nURf%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A9dpm%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqry2Jvh7kFTekQNNQUOXDUA1?pwd=936i</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>695695</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/40000.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>真人快打：遗产合集/Mortal Kombat: Legacy Kollection（更新v20260325）</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3454980/24fece3b770962ade1a94dfb3f134befe97469b9/header.jpg?t=1761854834</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=1GUldG1XhMt1ESIdaSk3QQ&amp;pwd=5ub3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=QB36V3qyqaQn%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A3x9s%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqrssKh3tNrfhwPqqiSU8T7A1?pwd=mqh6</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>998562</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/38028.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>孤独公会/The Lonesome Guild（更新v1.5.0）</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1486450/header.jpg?t=1761226441</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=4gDd2BZ9GtF0DWAJnLx2fw&amp;pwd=raup</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=6j22imFJJRJr%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aca09%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqrsKqzDHlkLphEAhjOpsc4A1?pwd=jxsw</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>697456</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/37901.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3D密室逃脱：遗产的诅咒/3D Escape Room: Cursed Legacy</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/4175140/64573e3c64f42959ae72d5906afd386724a99e97/header.jpg?t=1776239167</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=n6tLm9pzQvuAdt1zxb3loA&amp;pwd=btir</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=F7JZ32rqm63a%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Afph4%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqoXiYwq-S_mG2OCcXv6AuGA1?pwd=ax4f</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>598932</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39999.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>不要失去仇恨/Don’t Lose Aggro</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3079160/8c8d2d85d5bfe38d8d37809e7e82f692551306af/header.jpg?t=1776261677</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=4ZpdVK8nkXjkcYyy_w8SSA&amp;pwd=p2tn</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=Qf6RB3ENzYZr%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Az5hr%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqoX6kXW8CatkaIBGM5QdskA1?pwd=ruik</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>395689</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39998.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>帽中客/Hatters</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3612660/afff0cf833d8ed6205d83a87fe803fb713fa91f8/header.jpg?t=1776284115</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=JvT49cxEA_NQSE11EA6qvQ&amp;pwd=xiap</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=yuiUn23QNBv2%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Agk7n%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqoWJVNSNEiSpIe6iApOQx1A1?pwd=98ig</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>568923</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39997.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>灾难天使：特快专递/Calamity Angels: Special Delivery</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3974290/41d5521362866c0743cb881bab73b8dfbcb34616/header.jpg?t=1776272586</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=UPGEuC3HfSsN4FCi8IJrxA&amp;pwd=e5gr</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=U7nUVzBZZbym%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Afs3w%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqoVq0wbNMPfH2OzeSkJ7SLA1?pwd=tzwx</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>236598</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39996.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>憋不住了！/We Gotta Go</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3967470/b4b3b19ff53b06b1f1a3408cd953499f4334849e/header_schinese.jpg?t=1776436137</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=MWl01UWoX0u5oSW-587PgQ&amp;pwd=9vey</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=M3uaa2RNJzEf%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A1buu%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqoVACmh7kFTekQNNQSWqfOA1?pwd=asp3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>690690</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39995.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>电力拼拼乐/Electrogical</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2501650/a08a9cf368a289ffb46b9e8824a2241a4103cf3f/header_schinese.jpg?t=1776336473</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=gFbxK82j5c4DwZFGuRQXSQ&amp;pwd=24ge</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=AzaamaF3eiYf%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A9uef%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqoUaILv8NzspwJIMoq0w9WA1?pwd=xw9m</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>986532</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39994.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>回转寿司模拟器/Conveyor Belt Sushi Simulator</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3536670/8d256bd9fccc2f250a2cb9bd363709e74b4f37e5/header.jpg?t=1776322769</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=d4wRxoFU03OmNjnKdrU46g&amp;pwd=ms8g</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=mimQ3eU3yqYn%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Avx7m%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqoU5OMEA6EdR3k--IPtcZ-A1?pwd=zgxg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>889966</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39993.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>复古驱动器 改头换面/Retro Drive: Revamped</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2142380/eede10c9cc63373541347d2bc3e13ede310b5513/header.jpg?t=1774605027</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=KzoK01f11nu2Vz89drDpNg&amp;pwd=pmta</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=777NfizIbYv2%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A3vxv%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqoTXvZ30ndbepq4wzdk3PYA1?pwd=tf8w</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>986532</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39992.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>太空引擎/SpaceEngine（更新v0.991.50.2125）</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://media.st.dl.eccdnx.com/steam/apps/314650/header.jpg?t=1708470679</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=HAowZGzu7JqEXTDMmWNTLw&amp;pwd=pdsv</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=YBJvInUvemA3%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Atz20%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOQpyOb8wA-ePWAhoo1WDQHuA1?pwd=s5ia</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>139449</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/24052.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>动物收容所2/Animal Shelter 2（更新v1.2.3）</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2658510/header_schinese.jpg?t=1753436011</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=ZA2IzHkrr6_G4zfZs3LpBg&amp;pwd=axw2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=FjqqI3iQRjea%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A5loj%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOW0-oZ-5joeLDzu8J7Y8acxA1?pwd=yjs5</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>908070</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/35641.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>黑白莫比乌斯：岁月的代价/Monochrome Mobius: Rights and Wrongs Forgotten（更新Build.22628354）</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1962430/header.jpg?t=1732445114</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=0mu0Hazy7hLpKd-mhOLS-w&amp;pwd=vq82</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=zeIZZfvY3E3y%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A77lr%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOOC4KX6MUsM6i9cfJIQJMViA1?pwd=3yir</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>662145</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/32509.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>救命！怎么又塌了!/Haste（更新v1.11.a）</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1796470/7f0cbc96390382f5312ea01f9a8f1f17a064f4eb/header_schinese.jpg?t=1743519789</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=ZUE8Kpnj54bR9k40_zd13Q&amp;pwd=zy7x</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=iE73u2zMV7Jv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aibg2%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOMpeI121JcyzLJJIOqBCv6pA1?pwd=kt3j</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>669988</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/31766.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>萌族纪元/Animalkind</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2997840/49df789bc8e559fc4cba6a15b778b224c2152744/header_schinese.jpg?t=1776116992</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=JqQQYSBr7sjbewJRJsjJsg&amp;pwd=texk</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=zAbE7rZnmAbq%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ab1zn%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqmfvuXDHlkLphEAhjLx_u0A1?pwd=resq</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>963258</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39991.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>命运之弦11：魔法幻梦/Strings of Fate XI: Magic dream</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2965220/header.jpg?t=1774006180</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=KqvBzBe60BpBEFchRryvuA&amp;pwd=d2vy</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=EfARZrRBnAf2%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A9omi%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqmfSgRh7kFTekQNNQRVUu9A1?pwd=fwnz</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>856598</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39990.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>原爆点/Ground Zero</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2340130/26f2468a93a6ca6f6e65d80b6d4d9debdb0ef60e/header.jpg?t=1776352535</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=tb7p04x_ARIfCFQrs0DApQ&amp;pwd=jur6</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=VBJVni3IVBbi%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aorg7%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqmetjQ6NDRTnYcd9mJ1gJkA1?pwd=jru5</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>235689</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39989.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>香缇小镇/ShantyTown</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2434600/9c5821255a378fc361e2258122cf741c0b10b681/header.jpg?t=1776414388</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=KOAWtt2tmYr-4YKIkIb0Rg&amp;pwd=vfgx</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=I7RFNzb2Yvqi%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A8spv%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqjNeGGd7d9SmHoh0B2M3o_A1?pwd=28ii</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>336699</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39988.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>缮写室 ：羊皮卷大师/Scriptorium: Master of Manuscripts</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3119540/f78f1c1f943426314e9c434083b1e7e367c381c1/header_alt_assets_3_schinese.jpg?t=1776445731</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=EQUz-qYom3f8-E2gOxDgDg&amp;pwd=575a</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=6BRRbqi6fQ7j%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ah3mo%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqjN77R6NDRTnYcd9mHAdyOA1?pwd=kczj</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>236985</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39987.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>壁虎之神/Gecko Gods</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1290760/8ea6b1fdf0614973f2b441d077c1223ded59a4c6/header_schinese.jpg?t=1776761454</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=x8_481KjAdP0IspRgdUlcA&amp;pwd=b6yt</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=a2IZbyjYBZja%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A1huy%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqjMTZWLzINXYhK-TK9M0lqA1?pwd=ff8t</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>816255</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39986.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>清洁大作战！/Cleaning Up!</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3835650/e05382f1b6d3f8fb5c042d51e24591f1025ed253/header_schinese.jpg?t=1776700125</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=n-ah9TQf6400sSIshWshXw&amp;pwd=rjsi</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=vYVvAjZ7JBJv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ay3to%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqjLsu76NDRTnYcd9mH9ts9A1?pwd=puev</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>809098</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39985.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>瓦尔索斯：王位继承人/Varthos – Heir to the Throne</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3065870/6a5252682987f02d6bc9b640c335e241893fb42f/header.jpg?t=1771342052</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=RI0M_q85lXBQ6pHETEGkmQ&amp;pwd=8wr8</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=ZbI7zmEvaaEz%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aktr9%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqjLJ6Cs4D30TtXu7MumaAcA1?pwd=95p8</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>996633</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39984.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>废墟之城/Skid Cities</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1242630/7d6a478ad00023520124d5f696ef6ef32ee38f30/header.jpg?t=1767512665</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=o8p7omedyDz4DyazzIiPxg&amp;pwd=94tw</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=uABZreRjyuIr%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A9bgx%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqjKnjOgt3ysyHrRJzWjD7RA1?pwd=5hm9</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>998856</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39983.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>尖啸/Screamer/支持网络联机</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2814990/f4fba3a1edca44fbb2bd86c80340eb3de854102b/header.jpg?t=1774512017</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=2ZOc_A0n2EKWAwvpFf33EA&amp;pwd=dkfy</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=fmuqemAfya2u%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A8mr0%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqjKFGdbQR_DIvzxrXhU3JKA1?pwd=9dk6</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>526398</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39982.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>潜行者2：切尔诺贝利之心/S.T.A.L.K.E.R. 2: Heart of Chornobyl（更新v1.9.0）</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1643320/header.jpg?t=1732124346</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=LfbHyPQBh0o4ZxnIyiycCg&amp;pwd=rim5</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=aAFv2yJzARNn%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ac1br%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOMoUSWgSy9AmhStYoZZZVSHA1?pwd=bnuz</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>558447</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/26267.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>缺氧：眼冒金星/Oxygen Not Included（更新v722606）</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://shared.st.dl.eccdnx.com/store_item_assets/steam/apps/457140/header_schinese.jpg?t=1732554824</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=fyLrDp65OJMuL15pq5l5DA&amp;pwd=8ijx</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=UJ7jInbyIBry%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Amp83%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VONZFYvMPlGz9ZeaaToYk6R8A1?pwd=7hst</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>669336</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/28441.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>U型潜艇/德国水手/UBOAT（更新v2026.1）</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/494840/header.jpg</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=KtuoPcMXFXGvMEEqDR-_3g&amp;pwd=xrnh</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=vYF3IzJjuyMv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aza2x%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VONngTB9M3nEyir5D5mmErkmA1?pwd=irhv</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>725246</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/24350.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>克苏鲁：恐怖深渊/Cthulhu: The Cosmic Abyss</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2760560/1211a01280977ae98a94c455ca61b2244ed5bc2e/header_alt_assets_2.jpg?t=1776420654</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=w5swtf0mprz4JpzoxAdPeA&amp;pwd=21tr</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=j2ErQbmUnYJf%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Apx60%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqdbpcJ6J4a1HG2J6sGzhoOA1?pwd=xt34</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>669985</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39981.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>哥布林破坏者：渐进式塔防/Goblin Buster: Incremental Tower Defense</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2482250/9a7bc42f7f603359cd3b28c318020a80a8be9423/header.jpg?t=1776250654</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=vj_OOpCzWfzYWqabuGwjVQ&amp;pwd=7btx</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=UZzUjmVZfI3i%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ajgb6%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqdbGM5O7k-JihP3pS9PblNA1?pwd=zjxj</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>758595</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39980.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>预先号令/WARNO（更新v188908）</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.wanya.vip/wp-content/uploads/2023/11/1699637837-5d518828ff221e1.jpg</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=MJ_wAAeD3vajVyo1fHohdg&amp;pwd=f6b4</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=BbYfuyANja6j%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aem7w%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqdSDLIO7k-JihP3pS9IBmbA1?pwd=yg9r</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>445781</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/22201.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>霓虹地狱/Neon Inferno（更新Build.22769029）</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2957720/header.jpg?t=1763749497</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=YMui2sly7TmGz5yhCTrZRQ&amp;pwd=jdd1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=u6rUzmVjUFvi%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A4sjd%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOexxYiTQVDkHuAOAocriraOA1?pwd=kruk</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>506090</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/38401.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>吸血鬼幸存者/Vampire Survivors（更新v1.14.112）</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://cdn.akamai.steamstatic.com/steam/apps/1794680/ss_6c55afe36be2a7784bf18cb9b3218321ae2d10e5.600x338.jpg?t=1641494667</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=heg3ZYe1qJTL3UU38vHI9Q&amp;pwd=5nvf</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=iIJvmaA7R7ry%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Acfn9%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqcSo0iNJZolJiRX3j_EBskA1?pwd=wb5j</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>166783</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/1877.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>战锤40K：星际战士2/Warhammer 40,000: Space Marine 2（更新v12.3.0.1）</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2183900/header_schinese.jpg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=ib0fgW-0NYQCUcmzJCxNKg&amp;pwd=mph5</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=iINrEfvEF36n%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Af9n4%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOS7wwrfnXXgMhpUm7iiPCzYA1?pwd=mmj9</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>943583</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/24597.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>沙龙模拟器/Saloon Simulator（更新Build.22754291）</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/1876930/header.jpg?t=1753017755</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=RrUhaQWN-DnK5_edLW5NcQ&amp;pwd=vycm</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=vURrq2FRFBvq%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Awh1o%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOVet58MDDlk5sgLqi0YwrkNA1?pwd=masx</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>112256</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/35443.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>脑怪来袭！脑晶保卫战/Chip ‘n Clawz vs. The Brainioids（更新v1.0.24634）</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1332430/header.jpg?t=1756408749</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=HJCQ0v5K0K25mrAeikfQcQ&amp;pwd=kwdw</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=zYjy6jIJfUJr%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9App0c%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOYuEwxRfqXL7NZvs0oqRVZHA1?pwd=s5aw</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>663325</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/36639.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>机器人角斗场/Clone Drone in the Danger Zone（更新v1.9.0.114）</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/wp-content/uploads/2024/04/1713110273-069d3bb002acd8d.png</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=fRwxsOdNfZucsAboOIMqeA&amp;pwd=mypf</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=yiqMbe3uiaEn%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Axg9k%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VNxzvNbsGOdmO8hqVDaZqRnlA1?pwd=kfg7</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>454939</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/3048.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>黑暗草案/Draft of Darkness（更新Build.22548811）</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1380650/header.jpg?t=1734122696</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=8vOCt4yDYajIzj805dtr1w&amp;pwd=wn5i</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=YjEjyufyiu6z%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Abjf7%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOK-ug5Vnv1Zjap0_PFc7Q32A1?pwd=pm2t</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>698785</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/30779.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>深渊之印/Mark of the Deep（更新v2.2.1）</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1933370/header.jpg?t=1737945181</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=szhUYQamrDc2M8ko_yfGUQ&amp;pwd=9eep</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=BNRNjmZbeMra%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Auck0%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTMjfym6eEI31Pdu4uOUQlA1?pwd=44hu</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>225969</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/29952.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>灾变前夜/Dread Dawn（更新Build.22555120）</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2093920/header_schinese.jpg?t=1734957119</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=KqVvw8g4W9LmQoZnaD2dYw&amp;pwd=mgde</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=IfeA3mniaUba%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A753k%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOQfYuJp83OvKBAitjqmPllPA1?pwd=yb7v</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>608221</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/29473.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>恐鬼症/Phasmophobia（更新v0.16.1.2）</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/739630/header.jpg?t=1727019976</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=oRC4GvTPK0yH7pChI6jFRg&amp;pwd=3r2v</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=V7b6vyUNRrue%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Avt2r%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOTzOHLYYFo9NZVSQxQ81eCvA1?pwd=v6dm</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>665712</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/29404.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>黯潮/Grim Tides – Old School RPG</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2341030/220f6e7f212cc789e61fffcb145e68a2778575d9/header.jpg?t=1774539896</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=Zl93KmeBgEMSeszJOmP-GQ&amp;pwd=qu38</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=JfaqMjnYJbu2%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aob7w%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTJ6dHlFtMoru7OBlv9_8mA1?pwd=wbk2</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>256985</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39979.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OPUS：心相吾山/OPUS: Prism Peak</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1947910/5ef46371681ae1dc9c78fe4f74cf781229d471c2/header_schinese.jpg?t=1776347423</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=mHrGAGpJQHgp54JlvukwsA&amp;pwd=ushw</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=UFj2me2MBBJb%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Asej0%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTIbS7dIw7kwRnmHkznvr3A1?pwd=89m8</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>369885</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39978.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>罪托邦/Sintopia</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2213700/93a9a2b37637780a31075fd1ddb85758551913c7/header_schinese.jpg?t=1776357810</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=A4Gx6ljY2kcK_u8QUmsMfQ&amp;pwd=9eai</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=fAFfYfRfyuu2%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Atv1l%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTIAuy_iTAwaKK_BNeP9DZA1?pwd=9f6e</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>265986</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39977.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>神探杰克鼠/MOUSE: P.I. For Hire</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2416450/298ff2fc3f6a700d022b8d3ec58047f2b426be03/header.jpg?t=1776466362</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=O358zpMY8HLco3qAxNo44Q&amp;pwd=xdh3</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=UBR7NruUrYVv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A2fpk%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTHXPDgYf_JB8v0Re8sAX-A1?pwd=e8u5</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>223369</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39976.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>埃斯玛尔探险家/Explorers of Esmar</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3046740/c82890b2a98171312e9800cdc4eda014abfabdba/header.jpg?t=1776204619</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=Zz8bAAgG-XwKWrlx-wRuDw&amp;pwd=i6i4</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=eMBje2f2YR3m%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ah6ke%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTH1aYEYDAzCPyqo6z2_6-A1?pwd=4smq</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>670690</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39975.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>极限叉车3/Extreme Forklifting 3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3172570/c6daff139d0f9f3bc0b2caf90d129ae4d9b7ad5b/header.jpg?t=1776167736</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=EtQH2YqH__nx1EAyun9B2Q&amp;pwd=bjkm</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=fIbuMrvma2ui%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Asn2f%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTG_SYgYf_JB8v0Re8rduiA1?pwd=uewv</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>986532</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39974.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>不要玩这个/Don’t Play This</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3319120/07d1ccb485d61cb593b42e8932fecf03e18f4a9c/header.jpg?t=1776353186</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=f45q7ph7R3BnLm0yrGcUCw&amp;pwd=f1t2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=uU3Qja2Mvimq%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Apls8%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTCEUrm6eEI31Pdu4uIKM0A1?pwd=htbb</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>822669</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39973.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>风启之旅/Windrose/支持网络联机</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3041230/6c0d1a762a62736e6aa7eabad29bfece0846feae/header_schinese.jpg?t=1776158614</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=CYyDW2NJRRH6tolYgwZfAw&amp;pwd=usmw</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=UraiIjVfYVFb%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A9o2q%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqTBmDzwmWbrMNeegZ3FBjqA1?pwd=edwk</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>669988</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39972.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>吞噬DEVOUR（更新Build.22763919）</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://shared.cloudflare.steamstatic.com/store_item_assets/steam/apps/1274570/header.jpg?t=1730624650</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=_blJJ9G-JjCxK892ZucCTg&amp;pwd=dve1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=AF3AbyEBBjuu%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Axs3w%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VORsqqOxQUKtXVzBBbczAUcAA1?pwd=6p45</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>659552</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/5029.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>监狱模拟器/Prison Simulator（更新v1.4.3.30）</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>image/gif;base64,R0lGODlhAQABAAAAACH5BAEKAAEALAAAAAABAAEAAAICTAEAOw==</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=yrwg5XPHp4plwgME3HRgjA&amp;pwd=8888</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=eIVzeiFbAN3a%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A2mec%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqOXshr5Kd4wk_GrRshdANBA1?pwd=r87m</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>148413</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/20342.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>波与月夜之青莲/Bo: Path of the Teal Lotus（更新v1.2.7）</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/1614440/header.jpg</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=HXF1FsW5dQOk4ucfqI-wew&amp;pwd=8888</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=ERVBZn7ZZVry%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A5slx%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VO2ebSGY4ZQTtcgJ3PBFgs9YA1?pwd=3xvt</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>181542</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/24261.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>华夏山河/Chinese Frontiers（更新v2.2.2）</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1640820/0df59564da35e0ed0906e990908362c7126c3c08/header_schinese.jpg?t=1750340571</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=e80E_PEPuf2CcuqypozKLw&amp;pwd=76bx</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=7RZfUrYnyy22%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A53pw%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOTGDXrjI6bZQMOOjDIiQPq2A1?pwd=v5x6</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>489515</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/34577.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>无人深空/无人之地/No Man’s Sky（更新v6.30）</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://media.st.dl.eccdnx.com/steam/apps/275850/ss_f63aa791c0b270fb853e1a3b93876929052bec4a.600x338.jpg?t=1677079554</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=4Svepth92YtFwmFAMK9HiA&amp;pwd=nrt6</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=a67RZbzymQFz%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Abbe8%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOW3F7I94ftaxeUy77LplETDA1?pwd=dxq9</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>567483</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/13008.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>颂钟长鸣/Bellwright（更新v0.0.47654）</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://media.st.dl.eccdnx.com/steam/apps/1812450/header.jpg?t=1713946194</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=kdsr5m57eaEnE05-X3ULKA&amp;pwd=ck2b</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=aUfQ7v36Zrme%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aes0k%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqOOMjeTdv14O3bjFyfO-EtA1?pwd=9v5t</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>391462</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/24007.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>洗衣店模拟器/Laundering Simulator – Clean Cash and Laundry</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3432750/header.jpg?t=1776089023</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=dhvMTmlhnfv7tMDYYuIxqw&amp;pwd=r57q</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=qINVjqUNfMre%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Asmg5%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqO3fzMnWBS9rUgdBb7jMQfA1?pwd=jp8x</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>666888</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39971.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>战锤 40K：火焰战士 – 经典重发行版/Warhammer 40,000: Fire Warrior (Classic)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/4280930/54ffaf87b65203fba10292c1833d61affef6c5f6/header.jpg?t=1776098188</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=Bq5eEbTKFg1cDTKV2fhqlA&amp;pwd=q8k3</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=3IzEZfaUviym%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A8hka%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqO36bWVqBVUEQP4rgikncZA1?pwd=pgs6</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>235689</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39970.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>心入妙境/Elemental Realms</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2464740/header_schinese.jpg?t=1730789321</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=hDmgfcsmujKFRjvaHvMHmA&amp;pwd=b3wa</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=ymUnmuFZ7veq%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Arpt9%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqO2dfDKbZD6c8eU5gm4HT2A1?pwd=hvsk</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>552366</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39969.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>渔业公司/Fishing Inc</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/4126480/c24603a175a733043d803b6159e5d856c59a2bb6/header.jpg?t=1776258453</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=jnjK868r0NZ5iR3ccfPoTA&amp;pwd=r46k</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=aU3Uz2ri6biu%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Atw79%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqO1UQGkMHpI13PHzWXAMKcA1?pwd=unm9</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>663669</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39968.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>东方资志疏/Immortal Immanuel</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2861740/header.jpg?t=1737085764</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=5-pH4S4WAeYAKCSBs8hNWQ&amp;pwd=7qjd</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=Yjimqq7ZJ7Nz%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A981z%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqO0kLp0ftEgn8nVUDsbmBqA1?pwd=nv4u</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>262928</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39967.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>多边形冲击/POLY IMPULSE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2805260/c358c9e0c94d7b23aa5e0005bf1ee851f4a29cbb/header.jpg?t=1773845977</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=c39oCLG0PaRs-M3r4a8BFg&amp;pwd=erft</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=B3ma6vqaiyAv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Apz26%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqO0FhpgYf_JB8v0Re5lFCBA1?pwd=g5w2</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>116118</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39966.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>无望之海/Hopeless Sea</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2732210/cef1ec93d9ca5404eaef8ae2601924a9034a1a9b/header_schinese.jpg?t=1762707566</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=5Qo_o0HjoZHOG4f9odIxTQ&amp;pwd=ayn4</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=FvMnaqrUVnyu%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A1lzq%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqO-S-APPA9vEzzRe8t5CwVA1?pwd=jteq</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>660880</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39965.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>黄金矿主模拟器：阿拉斯加淘金热/Alaska Gold Fever</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1674200/14b473bd090bce5a25114669c2ef5eb0830d202c/header_alt_assets_2.jpg?t=1776332357</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=PvwJ0xBTpyKH-CEvPrpcHw&amp;pwd=ig46</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=zANRfi6f6vmy%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A8onk%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqNznIakMHpI13PHzWX99TNA1?pwd=7itz</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>595956</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39964.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>庞贝：遗产/Pompeii: The Legacy（更新Build.22710196）</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2632240/8c5a16635913dd4cda31d92509bf3e80fac4e2dd/header.jpg?t=1761677878</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=Q_HYiYLUgIQX7HGIw1USHA&amp;pwd=w1gc</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=2Qj2uaZbMFrq%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A3etw%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJnvtSWPn2ShJWxKaXZQFyA1?pwd=d4t6</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>181212</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/38441.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>咒术师学院/Spellcaster University（更新v1.06）</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://media.st.dl.eccdnx.com/steam/apps/895620/extras/Frise_5Personnages610.png?t=1623829039</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=7ABYQO_G1BsWgYiWHoNFuQ&amp;pwd=7m5e</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=aQZzEjNRVVby%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A6xgz%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJI6flZ23fenhXXcA6RKPAA1?pwd=fk6k</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>422761</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/7049.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>摩西与柏拉图：开往爪镇的末班列车/Moses &amp; Plato – Last Train to Clawville</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2230450/139b56006956893aba72d80228d17660b43de190/header.jpg?t=1776171832</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=WesvdhHxlmahoaNMGDqyXA&amp;pwd=26yj</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=nIjy2qmuyQze%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aymo4%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJA2ObQQrS5L_ECiTLM9ziA1?pwd=kfst</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>232325</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39963.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>废墟国度：符文之门/Regions of Ruin: Runegate</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/1375750/c8474560dd967fba2d5a535535ec0ca74cc17bb7/header_schinese.jpg?t=1776177107</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=2MNsqhEuyvg3wO9Y3-2xSw&amp;pwd=fu2b</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=vU7RfeUbqARv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Aw5qb%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ9G6rziLwqyDuuwrLqg9nA1?pwd=usz5</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>556326</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39962.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>一点视角/A Little Perspective</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3485300/969df3cb30ad522a44f833e17949eb6d817c0acb/header.jpg?t=1775235598</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=rDl4eK8Yy5I2b5nsSP3hdA&amp;pwd=m6jm</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=b22qa2ZfMzae%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Anab6%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ7ZSyvLdflXP8zqbxesmGA1?pwd=vkk8</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>985236</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39961.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SOG：越南/SOG: Vietnam</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3288050/header.jpg?t=1773849116</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=8RWbjrMPdKdkB4e-hJAEZQ&amp;pwd=fnrg</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=my6jeyaMVrme%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A2tq6%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ6_OAAjRmZBvjCJxiqyJ1A1?pwd=xwc5</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>556236</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39960.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>不受欢迎的地下城/Unwanted Dungeon</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3733160/16a8131ec410ec2034d71fc87a107dcf6512eb15/header.jpg?t=1775572805</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=RczEwz0H2VOMVH_nKk_HJQ&amp;pwd=nkdv</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=YfE3AvNFjqAz%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A1ktq%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ67mkRqp8eAYWCibeLurIA1?pwd=2svp</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>223698</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39959.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>泛宇宙捍卫者/Defenders of the Omniverse</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2461840/header.jpg?t=1728674693</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=edEoGRmD70oGrKX1Tl1uWw&amp;pwd=emu5</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=3mqU7rm63Avu%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A9w1o%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ5BJDvLdflXP8zqbxdh4wA1?pwd=m4ev</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>336699</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39958.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>弗洛伦斯/Florence</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/1102130/header.jpg?t=1729099629</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=rxrf7bGrRr-A88oTepOKqA&amp;pwd=8ky3</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=nInAZvbuYjAf%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Az8yt%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ4V8sJhcwfOTZ-M9v7H_wA1?pwd=8k5z</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>223366</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39957.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>敲敲打宝/Tap Tap Loot</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3959890/2964006f8b5a5f16a7f2324f6d2c2ccf4cef14a6/header_schinese.jpg?t=1776236724</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=q14yIj5fqKTjMwTHCdJGGQ&amp;pwd=ujwt</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=3QjeqmIfUNVv%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A6lmv%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ3GoAAKjmSRSj2NXOQyMtA1?pwd=zffs</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>650506</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39955.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>在我走之前/Before I Go</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2715870/856d76753f6a0ca5b0845fe5486482e44254246a/header.jpg?t=1776092413</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=GWp84roTJxDjNNvfyfzVlQ&amp;pwd=euph</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=M7zuInnUbMBn%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A0uam%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ1lvvPPA9vEzzRe8qD-d7A1?pwd=6bhf</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>996652</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39954.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>圣物深渊/Relic Abyss</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3017760/f46231ef089bde021c725cec40753a42befd84b2/header.jpg?t=1776175228</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=u_hVQgMKMSMxuk6lFHID1g&amp;pwd=simc</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=JrMv6rFbIZNr%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A5tpy%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ08bOp-3wkJOXfzZSN5DQA1?pwd=nmw3</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>526398</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39953.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>背包幸存者/Backpack Survivors</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2294780/9ba55c72b96cd1271e1f7f72e1827834241e1f60/header.jpg?t=1776063661</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=dk8cgQKDabcNQvNq2A9RPA&amp;pwd=ydbg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=QZFzaqba6vei%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ahmx9%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqJ-dy1lFtMoru7OBlp2izgA1?pwd=fxf7</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>985258</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39952.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>洗衣模拟器/Laundry Simulator 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3144450/header_schinese.jpg?t=1776099624</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=9LiG0LyPimMmjCaR6CTwsg&amp;pwd=n3h5</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=n6b2YrmY3aum%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Ac5zn%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqIztLbyBH5wzAl81aIE5g2A1?pwd=65ap</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>663322</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39951.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>迪斯科灯光下：80年代酒吧模拟器/Under the Disco Lights – 80’s Bar Simulator</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3700950/a8c4d19cc7e68eb01e061a4e2e19953bfef95c47/header.jpg?t=1776089868</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=jrPoaprTanG40lSZs_H7Xg&amp;pwd=g6un</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=NFbMr2Jfe2Qr%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9Awn2e%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqIrlNSV2vRn91Mo6VzWoOnA1?pwd=azt3</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>235689</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39950.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>炮艇之神/Gunboat God</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2511210/0bf5e3625ea163234a2dc26f2e1ddfa236e7212c/header.jpg?t=1776243222</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://pan.baidu.com/share/init?surl=urfkCaRfyUEnObgzHjQJRw&amp;pwd=a2ds</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://cloud.189.cn/web/share?code=e67vYjVrYfU3%EF%BC%88%E8%AE%BF%E9%97%AE%E7%A0%81%EF%BC%9A1nov%EF%BC%89</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://pan.xunlei.com/s/VOqIrI9pRqp8eAYWCibeEUn3A1?pwd=jsym</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>932558</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39949.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>拾取循环/Loot Loop</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3972320/958eeeee0ffc1e7541ec44572c38af36e786222a/header.jpg?t=1776191627</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=Mzk5NDgtMC02MDMyYjY5N2Mw</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=Mzk5NDgtMS02MDMyYjY5N2Mw</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=Mzk5NDgtMi02MDMyYjY5N2Mw</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>526398</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/39948.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>模拟铁路：铁路模拟器/SimRail – The Railway Simulator（更新v20260326）</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1422130/header.jpg?t=1734118551</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzA1ODItMC0wNWI1MGVkNjVi</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzA1ODItMS0wNWI1MGVkNjVi</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzA1ODItMi0wNWI1MGVkNjVi</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>889012</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/30582.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>云族裔/inZOI（更新v0.7.5）</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/2456740/header.jpg?t=1743141318</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE1OTktMC1hYTNiZjk4NDhj</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE1OTktMS1hYTNiZjk4NDhj</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE1OTktMi1hYTNiZjk4NDhj</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>262525</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/31599.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STORROR 专业跑酷/STORROR Parkour Pro（更新Build.22680172）</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/3125250/header.jpg?t=1743436374</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE3NjQtMC0wMDNjNGQzMDg3</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE3NjQtMS0wMDNjNGQzMDg3</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE3NjQtMi0wMDNjNGQzMDg3</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/31764.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>家里蹲/Pull Stay（更新v1.0.7）</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://shared.fastly.steamstatic.com/store_item_assets/steam/apps/1179890/420408d4f1514d6d6a0470c9901bc5b82d4c53d1/header.jpg?t=1743423168</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE3NjEtMC1kNGJmMTQzMWM4</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE3NjEtMS1kNGJmMTQzMWM4</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/goto?down=MzE3NjEtMi1kNGJmMTQzMWM4</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>669875</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.yyds567.com/31761.html</t>
         </is>
       </c>
     </row>
